--- a/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
+++ b/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="306">
   <si>
     <t>Nombres</t>
   </si>
@@ -41,31 +41,895 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>asdas</t>
-  </si>
-  <si>
-    <t>Salcedo</t>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Pérez</t>
   </si>
   <si>
     <t>DNI</t>
   </si>
   <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>21321</t>
-  </si>
-  <si>
-    <t>ADMINISTRADOR</t>
-  </si>
-  <si>
-    <t>12231</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>1231221</t>
+    <t>12345678</t>
+  </si>
+  <si>
+    <t>987654321</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>juanperez</t>
+  </si>
+  <si>
+    <t>pass123</t>
+  </si>
+  <si>
+    <t>juan.perez@email.com</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>González</t>
+  </si>
+  <si>
+    <t>PASAPORTE</t>
+  </si>
+  <si>
+    <t>P987654321</t>
+  </si>
+  <si>
+    <t>987654322</t>
+  </si>
+  <si>
+    <t>DOCENTE</t>
+  </si>
+  <si>
+    <t>anagonzalez</t>
+  </si>
+  <si>
+    <t>ana.gonzalez@email.com</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>23456789</t>
+  </si>
+  <si>
+    <t>987654323</t>
+  </si>
+  <si>
+    <t>luismartinez</t>
+  </si>
+  <si>
+    <t>luis.martinez@email.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>P123456789</t>
+  </si>
+  <si>
+    <t>987654324</t>
+  </si>
+  <si>
+    <t>carloshernandez</t>
+  </si>
+  <si>
+    <t>carlos.hernandez@email.com</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>López</t>
+  </si>
+  <si>
+    <t>34567890</t>
+  </si>
+  <si>
+    <t>987654325</t>
+  </si>
+  <si>
+    <t>marialopez</t>
+  </si>
+  <si>
+    <t>maria.lopez@email.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Gómez</t>
+  </si>
+  <si>
+    <t>P234567890</t>
+  </si>
+  <si>
+    <t>987654326</t>
+  </si>
+  <si>
+    <t>pedrogomez</t>
+  </si>
+  <si>
+    <t>pedro.gomez@email.com</t>
+  </si>
+  <si>
+    <t>Sofía</t>
+  </si>
+  <si>
+    <t>Díaz</t>
+  </si>
+  <si>
+    <t>45678901</t>
+  </si>
+  <si>
+    <t>987654327</t>
+  </si>
+  <si>
+    <t>sofiadiaz</t>
+  </si>
+  <si>
+    <t>sofia.diaz@email.com</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Vázquez</t>
+  </si>
+  <si>
+    <t>P345678901</t>
+  </si>
+  <si>
+    <t>987654328</t>
+  </si>
+  <si>
+    <t>davidvazquez</t>
+  </si>
+  <si>
+    <t>david.vazquez@email.com</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Fernández</t>
+  </si>
+  <si>
+    <t>56789012</t>
+  </si>
+  <si>
+    <t>987654329</t>
+  </si>
+  <si>
+    <t>laurafernandez</t>
+  </si>
+  <si>
+    <t>laura.fernandez@email.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Sánchez</t>
+  </si>
+  <si>
+    <t>P456789012</t>
+  </si>
+  <si>
+    <t>987654330</t>
+  </si>
+  <si>
+    <t>miguelsanchez</t>
+  </si>
+  <si>
+    <t>miguel.sanchez@email.com</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Ramírez</t>
+  </si>
+  <si>
+    <t>67890123</t>
+  </si>
+  <si>
+    <t>987654331</t>
+  </si>
+  <si>
+    <t>saramirez</t>
+  </si>
+  <si>
+    <t>sara.ramirez@email.com</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>Jiménez</t>
+  </si>
+  <si>
+    <t>P567890123</t>
+  </si>
+  <si>
+    <t>987654332</t>
+  </si>
+  <si>
+    <t>josejimenez</t>
+  </si>
+  <si>
+    <t>jose.jimenez@email.com</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
+  </si>
+  <si>
+    <t>78901234</t>
+  </si>
+  <si>
+    <t>987654333</t>
+  </si>
+  <si>
+    <t>isabelruiz</t>
+  </si>
+  <si>
+    <t>isabel.ruiz@email.com</t>
+  </si>
+  <si>
+    <t>Raúl</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>P678901234</t>
+  </si>
+  <si>
+    <t>987654334</t>
+  </si>
+  <si>
+    <t>raultorres</t>
+  </si>
+  <si>
+    <t>raul.torres@email.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>Álvarez</t>
+  </si>
+  <si>
+    <t>89012345</t>
+  </si>
+  <si>
+    <t>987654335</t>
+  </si>
+  <si>
+    <t>carmenalvarez</t>
+  </si>
+  <si>
+    <t>carmen.alvarez@email.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>Gil</t>
+  </si>
+  <si>
+    <t>P789012345</t>
+  </si>
+  <si>
+    <t>987654336</t>
+  </si>
+  <si>
+    <t>javiergil</t>
+  </si>
+  <si>
+    <t>javier.gil@email.com</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Molina</t>
+  </si>
+  <si>
+    <t>90123456</t>
+  </si>
+  <si>
+    <t>987654337</t>
+  </si>
+  <si>
+    <t>elenamolina</t>
+  </si>
+  <si>
+    <t>elena.molina@email.com</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>Suárez</t>
+  </si>
+  <si>
+    <t>P890123456</t>
+  </si>
+  <si>
+    <t>987654338</t>
+  </si>
+  <si>
+    <t>manuelsuarez</t>
+  </si>
+  <si>
+    <t>manuel.suarez@email.com</t>
+  </si>
+  <si>
+    <t>Martín</t>
+  </si>
+  <si>
+    <t>Moreno</t>
+  </si>
+  <si>
+    <t>12345679</t>
+  </si>
+  <si>
+    <t>987654339</t>
+  </si>
+  <si>
+    <t>martinmoreno</t>
+  </si>
+  <si>
+    <t>martin.moreno@email.com</t>
+  </si>
+  <si>
+    <t>Paula</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>P234567891</t>
+  </si>
+  <si>
+    <t>987654340</t>
+  </si>
+  <si>
+    <t>paulamunoz</t>
+  </si>
+  <si>
+    <t>paula.munoz@email.com</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>Méndez</t>
+  </si>
+  <si>
+    <t>23456780</t>
+  </si>
+  <si>
+    <t>987654341</t>
+  </si>
+  <si>
+    <t>antoniomendez</t>
+  </si>
+  <si>
+    <t>antonio.mendez@email.com</t>
+  </si>
+  <si>
+    <t>Clara</t>
+  </si>
+  <si>
+    <t>Serrano</t>
+  </si>
+  <si>
+    <t>P345678902</t>
+  </si>
+  <si>
+    <t>987654342</t>
+  </si>
+  <si>
+    <t>claraserrano</t>
+  </si>
+  <si>
+    <t>clara.serrano@email.com</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>Ortíz</t>
+  </si>
+  <si>
+    <t>34567891</t>
+  </si>
+  <si>
+    <t>987654343</t>
+  </si>
+  <si>
+    <t>fernandoortiz</t>
+  </si>
+  <si>
+    <t>fernando.ortiz@email.com</t>
+  </si>
+  <si>
+    <t>Beatriz</t>
+  </si>
+  <si>
+    <t>Crespo</t>
+  </si>
+  <si>
+    <t>P456789013</t>
+  </si>
+  <si>
+    <t>987654344</t>
+  </si>
+  <si>
+    <t>beatrizcrespo</t>
+  </si>
+  <si>
+    <t>beatriz.crespo@email.com</t>
+  </si>
+  <si>
+    <t>Raquel</t>
+  </si>
+  <si>
+    <t>García</t>
+  </si>
+  <si>
+    <t>45678902</t>
+  </si>
+  <si>
+    <t>987654345</t>
+  </si>
+  <si>
+    <t>raquelgarcia</t>
+  </si>
+  <si>
+    <t>raquel.garcia@email.com</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>P567890124</t>
+  </si>
+  <si>
+    <t>987654346</t>
+  </si>
+  <si>
+    <t>francisconavarro</t>
+  </si>
+  <si>
+    <t>francisco.navarro@email.com</t>
+  </si>
+  <si>
+    <t>Ángel</t>
+  </si>
+  <si>
+    <t>Romero</t>
+  </si>
+  <si>
+    <t>56789013</t>
+  </si>
+  <si>
+    <t>987654347</t>
+  </si>
+  <si>
+    <t>angelromero</t>
+  </si>
+  <si>
+    <t>angel.romero@email.com</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>Paredes</t>
+  </si>
+  <si>
+    <t>P678901235</t>
+  </si>
+  <si>
+    <t>987654348</t>
+  </si>
+  <si>
+    <t>teresaparedes</t>
+  </si>
+  <si>
+    <t>teresa.paredes@email.com</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>Castro</t>
+  </si>
+  <si>
+    <t>67890124</t>
+  </si>
+  <si>
+    <t>987654349</t>
+  </si>
+  <si>
+    <t>rosacastro</t>
+  </si>
+  <si>
+    <t>rosa.castro@email.com</t>
+  </si>
+  <si>
+    <t>Víctor</t>
+  </si>
+  <si>
+    <t>Salazar</t>
+  </si>
+  <si>
+    <t>P789012346</t>
+  </si>
+  <si>
+    <t>987654350</t>
+  </si>
+  <si>
+    <t>victorsalazar</t>
+  </si>
+  <si>
+    <t>victor.salazar@email.com</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>78901235</t>
+  </si>
+  <si>
+    <t>987654351</t>
+  </si>
+  <si>
+    <t>adrianasantos</t>
+  </si>
+  <si>
+    <t>adriana.santos@email.com</t>
+  </si>
+  <si>
+    <t>Tomás</t>
+  </si>
+  <si>
+    <t>Gutiérrez</t>
+  </si>
+  <si>
+    <t>P890123457</t>
+  </si>
+  <si>
+    <t>987654352</t>
+  </si>
+  <si>
+    <t>tomasgutierrez</t>
+  </si>
+  <si>
+    <t>tomas.gutierrez@email.com</t>
+  </si>
+  <si>
+    <t>Verónica</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>89012346</t>
+  </si>
+  <si>
+    <t>987654353</t>
+  </si>
+  <si>
+    <t>veronicaluna</t>
+  </si>
+  <si>
+    <t>veronica.luna@email.com</t>
+  </si>
+  <si>
+    <t>Óscar</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>P901234568</t>
+  </si>
+  <si>
+    <t>987654354</t>
+  </si>
+  <si>
+    <t>oscarvega</t>
+  </si>
+  <si>
+    <t>oscar.vega@email.com</t>
+  </si>
+  <si>
+    <t>Luisana</t>
+  </si>
+  <si>
+    <t>Ponce</t>
+  </si>
+  <si>
+    <t>12345680</t>
+  </si>
+  <si>
+    <t>987654355</t>
+  </si>
+  <si>
+    <t>luisanaponce</t>
+  </si>
+  <si>
+    <t>luisana.ponce@email.com</t>
+  </si>
+  <si>
+    <t>Esteban</t>
+  </si>
+  <si>
+    <t>Herrera</t>
+  </si>
+  <si>
+    <t>P234567892</t>
+  </si>
+  <si>
+    <t>987654356</t>
+  </si>
+  <si>
+    <t>estebanherrera</t>
+  </si>
+  <si>
+    <t>esteban.herrera@email.com</t>
+  </si>
+  <si>
+    <t>Dolores</t>
+  </si>
+  <si>
+    <t>23456781</t>
+  </si>
+  <si>
+    <t>987654357</t>
+  </si>
+  <si>
+    <t>doloresjimenez</t>
+  </si>
+  <si>
+    <t>dolores.jimenez@email.com</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Castillo</t>
+  </si>
+  <si>
+    <t>P345678903</t>
+  </si>
+  <si>
+    <t>987654358</t>
+  </si>
+  <si>
+    <t>evacastillo</t>
+  </si>
+  <si>
+    <t>eva.castillo@email.com</t>
+  </si>
+  <si>
+    <t>César</t>
+  </si>
+  <si>
+    <t>Rojas</t>
+  </si>
+  <si>
+    <t>34567892</t>
+  </si>
+  <si>
+    <t>987654359</t>
+  </si>
+  <si>
+    <t>cesarrojas</t>
+  </si>
+  <si>
+    <t>cesar.rojas@email.com</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>P456789014</t>
+  </si>
+  <si>
+    <t>987654360</t>
+  </si>
+  <si>
+    <t>gabrielagonzalez</t>
+  </si>
+  <si>
+    <t>gabriela.gonzalez@email.com</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>45678903</t>
+  </si>
+  <si>
+    <t>987654361</t>
+  </si>
+  <si>
+    <t>rafaelhidalgo</t>
+  </si>
+  <si>
+    <t>rafael.hidalgo@email.com</t>
+  </si>
+  <si>
+    <t>Lorena</t>
+  </si>
+  <si>
+    <t>Cordero</t>
+  </si>
+  <si>
+    <t>P567890125</t>
+  </si>
+  <si>
+    <t>987654362</t>
+  </si>
+  <si>
+    <t>lorenacordero</t>
+  </si>
+  <si>
+    <t>lorena.cordero@email.com</t>
+  </si>
+  <si>
+    <t>Juan José</t>
+  </si>
+  <si>
+    <t>Campos</t>
+  </si>
+  <si>
+    <t>56789014</t>
+  </si>
+  <si>
+    <t>987654363</t>
+  </si>
+  <si>
+    <t>juanjosecampos</t>
+  </si>
+  <si>
+    <t>juan.jose.campos@email.com</t>
+  </si>
+  <si>
+    <t>Marta</t>
+  </si>
+  <si>
+    <t>P678901236</t>
+  </si>
+  <si>
+    <t>987654364</t>
+  </si>
+  <si>
+    <t>martaruiz</t>
+  </si>
+  <si>
+    <t>marta.ruiz@email.com</t>
+  </si>
+  <si>
+    <t>Emilia</t>
+  </si>
+  <si>
+    <t>67890125</t>
+  </si>
+  <si>
+    <t>987654365</t>
+  </si>
+  <si>
+    <t>emiliasanchez</t>
+  </si>
+  <si>
+    <t>emilia.sanchez@email.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>Rodríguez</t>
+  </si>
+  <si>
+    <t>P789012347</t>
+  </si>
+  <si>
+    <t>987654366</t>
+  </si>
+  <si>
+    <t>alfonsorodriguez</t>
+  </si>
+  <si>
+    <t>alfonso.rodriguez@email.com</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>78901236</t>
+  </si>
+  <si>
+    <t>987654367</t>
+  </si>
+  <si>
+    <t>veronicamorales</t>
+  </si>
+  <si>
+    <t>veronica.morales@email.com</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>P890123458</t>
+  </si>
+  <si>
+    <t>987654368</t>
+  </si>
+  <si>
+    <t>pablorodriguez</t>
+  </si>
+  <si>
+    <t>pablo.rodriguez@email.com</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>90123457</t>
+  </si>
+  <si>
+    <t>987654369</t>
+  </si>
+  <si>
+    <t>marcosjimenez</t>
+  </si>
+  <si>
+    <t>marcos.jimenez@email.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>P901234569</t>
+  </si>
+  <si>
+    <t>987654370</t>
+  </si>
+  <si>
+    <t>silviaperez</t>
+  </si>
+  <si>
+    <t>silvia.perez@email.com</t>
   </si>
 </sst>
 </file>
@@ -110,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -182,6 +1046,1427 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30" t="s">
+        <v>185</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" t="s">
+        <v>198</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>204</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
+        <v>210</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" t="s">
+        <v>215</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>216</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" t="s">
+        <v>222</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
+        <v>226</v>
+      </c>
+      <c r="E37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38" t="s">
+        <v>232</v>
+      </c>
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" t="s">
+        <v>233</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>239</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>241</v>
+      </c>
+      <c r="B40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
+        <v>245</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>247</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>250</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>254</v>
+      </c>
+      <c r="E42" t="s">
+        <v>255</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
+        <v>256</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>258</v>
+      </c>
+      <c r="B43" t="s">
+        <v>259</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>260</v>
+      </c>
+      <c r="E43" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>262</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>264</v>
+      </c>
+      <c r="B44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>273</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>275</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" t="s">
+        <v>277</v>
+      </c>
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>282</v>
+      </c>
+      <c r="E47" t="s">
+        <v>283</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>284</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>206</v>
+      </c>
+      <c r="B48" t="s">
+        <v>286</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" t="s">
+        <v>289</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
+        <v>292</v>
+      </c>
+      <c r="E49" t="s">
+        <v>293</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>294</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>296</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>297</v>
+      </c>
+      <c r="E50" t="s">
+        <v>298</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" t="s">
+        <v>299</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" t="s">
+        <v>302</v>
+      </c>
+      <c r="E51" t="s">
+        <v>303</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>304</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
+++ b/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="306">
   <si>
     <t>Nombres</t>
   </si>
@@ -41,31 +41,895 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>Marco Alexandre</t>
-  </si>
-  <si>
-    <t>Zarate Zavaleta</t>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Pérez</t>
   </si>
   <si>
     <t>DNI</t>
   </si>
   <si>
-    <t>72942023</t>
-  </si>
-  <si>
-    <t>987456654</t>
+    <t>12345678</t>
+  </si>
+  <si>
+    <t>987654321</t>
   </si>
   <si>
     <t>ADMIN</t>
   </si>
   <si>
-    <t>Val</t>
-  </si>
-  <si>
-    <t>050305</t>
-  </si>
-  <si>
-    <t>zaratemarcounfv@gmail.com</t>
+    <t>juanperez</t>
+  </si>
+  <si>
+    <t>pass123</t>
+  </si>
+  <si>
+    <t>juan.perez@email.com</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>González</t>
+  </si>
+  <si>
+    <t>PASAPORTE</t>
+  </si>
+  <si>
+    <t>P987654321</t>
+  </si>
+  <si>
+    <t>987654322</t>
+  </si>
+  <si>
+    <t>DOCENTE</t>
+  </si>
+  <si>
+    <t>anagonzalez</t>
+  </si>
+  <si>
+    <t>ana.gonzalez@email.com</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>23456789</t>
+  </si>
+  <si>
+    <t>987654323</t>
+  </si>
+  <si>
+    <t>luismartinez</t>
+  </si>
+  <si>
+    <t>luis.martinez@email.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>P123456789</t>
+  </si>
+  <si>
+    <t>987654324</t>
+  </si>
+  <si>
+    <t>carloshernandez</t>
+  </si>
+  <si>
+    <t>carlos.hernandez@email.com</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>López</t>
+  </si>
+  <si>
+    <t>34567890</t>
+  </si>
+  <si>
+    <t>987654325</t>
+  </si>
+  <si>
+    <t>marialopez</t>
+  </si>
+  <si>
+    <t>maria.lopez@email.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Gómez</t>
+  </si>
+  <si>
+    <t>P234567890</t>
+  </si>
+  <si>
+    <t>987654326</t>
+  </si>
+  <si>
+    <t>pedrogomez</t>
+  </si>
+  <si>
+    <t>pedro.gomez@email.com</t>
+  </si>
+  <si>
+    <t>Sofía</t>
+  </si>
+  <si>
+    <t>Díaz</t>
+  </si>
+  <si>
+    <t>45678901</t>
+  </si>
+  <si>
+    <t>987654327</t>
+  </si>
+  <si>
+    <t>sofiadiaz</t>
+  </si>
+  <si>
+    <t>sofia.diaz@email.com</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Vázquez</t>
+  </si>
+  <si>
+    <t>P345678901</t>
+  </si>
+  <si>
+    <t>987654328</t>
+  </si>
+  <si>
+    <t>davidvazquez</t>
+  </si>
+  <si>
+    <t>david.vazquez@email.com</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Fernández</t>
+  </si>
+  <si>
+    <t>56789012</t>
+  </si>
+  <si>
+    <t>987654329</t>
+  </si>
+  <si>
+    <t>laurafernandez</t>
+  </si>
+  <si>
+    <t>laura.fernandez@email.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Sánchez</t>
+  </si>
+  <si>
+    <t>P456789012</t>
+  </si>
+  <si>
+    <t>987654330</t>
+  </si>
+  <si>
+    <t>miguelsanchez</t>
+  </si>
+  <si>
+    <t>miguel.sanchez@email.com</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Ramírez</t>
+  </si>
+  <si>
+    <t>67890123</t>
+  </si>
+  <si>
+    <t>987654331</t>
+  </si>
+  <si>
+    <t>saramirez</t>
+  </si>
+  <si>
+    <t>sara.ramirez@email.com</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>Jiménez</t>
+  </si>
+  <si>
+    <t>P567890123</t>
+  </si>
+  <si>
+    <t>987654332</t>
+  </si>
+  <si>
+    <t>josejimenez</t>
+  </si>
+  <si>
+    <t>jose.jimenez@email.com</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
+  </si>
+  <si>
+    <t>78901234</t>
+  </si>
+  <si>
+    <t>987654333</t>
+  </si>
+  <si>
+    <t>isabelruiz</t>
+  </si>
+  <si>
+    <t>isabel.ruiz@email.com</t>
+  </si>
+  <si>
+    <t>Raúl</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>P678901234</t>
+  </si>
+  <si>
+    <t>987654334</t>
+  </si>
+  <si>
+    <t>raultorres</t>
+  </si>
+  <si>
+    <t>raul.torres@email.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>Álvarez</t>
+  </si>
+  <si>
+    <t>89012345</t>
+  </si>
+  <si>
+    <t>987654335</t>
+  </si>
+  <si>
+    <t>carmenalvarez</t>
+  </si>
+  <si>
+    <t>carmen.alvarez@email.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>Gil</t>
+  </si>
+  <si>
+    <t>P789012345</t>
+  </si>
+  <si>
+    <t>987654336</t>
+  </si>
+  <si>
+    <t>javiergil</t>
+  </si>
+  <si>
+    <t>javier.gil@email.com</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Molina</t>
+  </si>
+  <si>
+    <t>90123456</t>
+  </si>
+  <si>
+    <t>987654337</t>
+  </si>
+  <si>
+    <t>elenamolina</t>
+  </si>
+  <si>
+    <t>elena.molina@email.com</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>Suárez</t>
+  </si>
+  <si>
+    <t>P890123456</t>
+  </si>
+  <si>
+    <t>987654338</t>
+  </si>
+  <si>
+    <t>manuelsuarez</t>
+  </si>
+  <si>
+    <t>manuel.suarez@email.com</t>
+  </si>
+  <si>
+    <t>Martín</t>
+  </si>
+  <si>
+    <t>Moreno</t>
+  </si>
+  <si>
+    <t>12345679</t>
+  </si>
+  <si>
+    <t>987654339</t>
+  </si>
+  <si>
+    <t>martinmoreno</t>
+  </si>
+  <si>
+    <t>martin.moreno@email.com</t>
+  </si>
+  <si>
+    <t>Paula</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>P234567891</t>
+  </si>
+  <si>
+    <t>987654340</t>
+  </si>
+  <si>
+    <t>paulamunoz</t>
+  </si>
+  <si>
+    <t>paula.munoz@email.com</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>Méndez</t>
+  </si>
+  <si>
+    <t>23456780</t>
+  </si>
+  <si>
+    <t>987654341</t>
+  </si>
+  <si>
+    <t>antoniomendez</t>
+  </si>
+  <si>
+    <t>antonio.mendez@email.com</t>
+  </si>
+  <si>
+    <t>Clara</t>
+  </si>
+  <si>
+    <t>Serrano</t>
+  </si>
+  <si>
+    <t>P345678902</t>
+  </si>
+  <si>
+    <t>987654342</t>
+  </si>
+  <si>
+    <t>claraserrano</t>
+  </si>
+  <si>
+    <t>clara.serrano@email.com</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>Ortíz</t>
+  </si>
+  <si>
+    <t>34567891</t>
+  </si>
+  <si>
+    <t>987654343</t>
+  </si>
+  <si>
+    <t>fernandoortiz</t>
+  </si>
+  <si>
+    <t>fernando.ortiz@email.com</t>
+  </si>
+  <si>
+    <t>Beatriz</t>
+  </si>
+  <si>
+    <t>Crespo</t>
+  </si>
+  <si>
+    <t>P456789013</t>
+  </si>
+  <si>
+    <t>987654344</t>
+  </si>
+  <si>
+    <t>beatrizcrespo</t>
+  </si>
+  <si>
+    <t>beatriz.crespo@email.com</t>
+  </si>
+  <si>
+    <t>Raquel</t>
+  </si>
+  <si>
+    <t>García</t>
+  </si>
+  <si>
+    <t>45678902</t>
+  </si>
+  <si>
+    <t>987654345</t>
+  </si>
+  <si>
+    <t>raquelgarcia</t>
+  </si>
+  <si>
+    <t>raquel.garcia@email.com</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>P567890124</t>
+  </si>
+  <si>
+    <t>987654346</t>
+  </si>
+  <si>
+    <t>francisconavarro</t>
+  </si>
+  <si>
+    <t>francisco.navarro@email.com</t>
+  </si>
+  <si>
+    <t>Ángel</t>
+  </si>
+  <si>
+    <t>Romero</t>
+  </si>
+  <si>
+    <t>56789013</t>
+  </si>
+  <si>
+    <t>987654347</t>
+  </si>
+  <si>
+    <t>angelromero</t>
+  </si>
+  <si>
+    <t>angel.romero@email.com</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>Paredes</t>
+  </si>
+  <si>
+    <t>P678901235</t>
+  </si>
+  <si>
+    <t>987654348</t>
+  </si>
+  <si>
+    <t>teresaparedes</t>
+  </si>
+  <si>
+    <t>teresa.paredes@email.com</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>Castro</t>
+  </si>
+  <si>
+    <t>67890124</t>
+  </si>
+  <si>
+    <t>987654349</t>
+  </si>
+  <si>
+    <t>rosacastro</t>
+  </si>
+  <si>
+    <t>rosa.castro@email.com</t>
+  </si>
+  <si>
+    <t>Víctor</t>
+  </si>
+  <si>
+    <t>Salazar</t>
+  </si>
+  <si>
+    <t>P789012346</t>
+  </si>
+  <si>
+    <t>987654350</t>
+  </si>
+  <si>
+    <t>victorsalazar</t>
+  </si>
+  <si>
+    <t>victor.salazar@email.com</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>78901235</t>
+  </si>
+  <si>
+    <t>987654351</t>
+  </si>
+  <si>
+    <t>adrianasantos</t>
+  </si>
+  <si>
+    <t>adriana.santos@email.com</t>
+  </si>
+  <si>
+    <t>Tomás</t>
+  </si>
+  <si>
+    <t>Gutiérrez</t>
+  </si>
+  <si>
+    <t>P890123457</t>
+  </si>
+  <si>
+    <t>987654352</t>
+  </si>
+  <si>
+    <t>tomasgutierrez</t>
+  </si>
+  <si>
+    <t>tomas.gutierrez@email.com</t>
+  </si>
+  <si>
+    <t>Verónica</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>89012346</t>
+  </si>
+  <si>
+    <t>987654353</t>
+  </si>
+  <si>
+    <t>veronicaluna</t>
+  </si>
+  <si>
+    <t>veronica.luna@email.com</t>
+  </si>
+  <si>
+    <t>Óscar</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>P901234568</t>
+  </si>
+  <si>
+    <t>987654354</t>
+  </si>
+  <si>
+    <t>oscarvega</t>
+  </si>
+  <si>
+    <t>oscar.vega@email.com</t>
+  </si>
+  <si>
+    <t>Luisana</t>
+  </si>
+  <si>
+    <t>Ponce</t>
+  </si>
+  <si>
+    <t>12345680</t>
+  </si>
+  <si>
+    <t>987654355</t>
+  </si>
+  <si>
+    <t>luisanaponce</t>
+  </si>
+  <si>
+    <t>luisana.ponce@email.com</t>
+  </si>
+  <si>
+    <t>Esteban</t>
+  </si>
+  <si>
+    <t>Herrera</t>
+  </si>
+  <si>
+    <t>P234567892</t>
+  </si>
+  <si>
+    <t>987654356</t>
+  </si>
+  <si>
+    <t>estebanherrera</t>
+  </si>
+  <si>
+    <t>esteban.herrera@email.com</t>
+  </si>
+  <si>
+    <t>Dolores</t>
+  </si>
+  <si>
+    <t>23456781</t>
+  </si>
+  <si>
+    <t>987654357</t>
+  </si>
+  <si>
+    <t>doloresjimenez</t>
+  </si>
+  <si>
+    <t>dolores.jimenez@email.com</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Castillo</t>
+  </si>
+  <si>
+    <t>P345678903</t>
+  </si>
+  <si>
+    <t>987654358</t>
+  </si>
+  <si>
+    <t>evacastillo</t>
+  </si>
+  <si>
+    <t>eva.castillo@email.com</t>
+  </si>
+  <si>
+    <t>César</t>
+  </si>
+  <si>
+    <t>Rojas</t>
+  </si>
+  <si>
+    <t>34567892</t>
+  </si>
+  <si>
+    <t>987654359</t>
+  </si>
+  <si>
+    <t>cesarrojas</t>
+  </si>
+  <si>
+    <t>cesar.rojas@email.com</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>P456789014</t>
+  </si>
+  <si>
+    <t>987654360</t>
+  </si>
+  <si>
+    <t>gabrielagonzalez</t>
+  </si>
+  <si>
+    <t>gabriela.gonzalez@email.com</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>45678903</t>
+  </si>
+  <si>
+    <t>987654361</t>
+  </si>
+  <si>
+    <t>rafaelhidalgo</t>
+  </si>
+  <si>
+    <t>rafael.hidalgo@email.com</t>
+  </si>
+  <si>
+    <t>Lorena</t>
+  </si>
+  <si>
+    <t>Cordero</t>
+  </si>
+  <si>
+    <t>P567890125</t>
+  </si>
+  <si>
+    <t>987654362</t>
+  </si>
+  <si>
+    <t>lorenacordero</t>
+  </si>
+  <si>
+    <t>lorena.cordero@email.com</t>
+  </si>
+  <si>
+    <t>Juan José</t>
+  </si>
+  <si>
+    <t>Campos</t>
+  </si>
+  <si>
+    <t>56789014</t>
+  </si>
+  <si>
+    <t>987654363</t>
+  </si>
+  <si>
+    <t>juanjosecampos</t>
+  </si>
+  <si>
+    <t>juan.jose.campos@email.com</t>
+  </si>
+  <si>
+    <t>Marta</t>
+  </si>
+  <si>
+    <t>P678901236</t>
+  </si>
+  <si>
+    <t>987654364</t>
+  </si>
+  <si>
+    <t>martaruiz</t>
+  </si>
+  <si>
+    <t>marta.ruiz@email.com</t>
+  </si>
+  <si>
+    <t>Emilia</t>
+  </si>
+  <si>
+    <t>67890125</t>
+  </si>
+  <si>
+    <t>987654365</t>
+  </si>
+  <si>
+    <t>emiliasanchez</t>
+  </si>
+  <si>
+    <t>emilia.sanchez@email.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>Rodríguez</t>
+  </si>
+  <si>
+    <t>P789012347</t>
+  </si>
+  <si>
+    <t>987654366</t>
+  </si>
+  <si>
+    <t>alfonsorodriguez</t>
+  </si>
+  <si>
+    <t>alfonso.rodriguez@email.com</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>78901236</t>
+  </si>
+  <si>
+    <t>987654367</t>
+  </si>
+  <si>
+    <t>veronicamorales</t>
+  </si>
+  <si>
+    <t>veronica.morales@email.com</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>P890123458</t>
+  </si>
+  <si>
+    <t>987654368</t>
+  </si>
+  <si>
+    <t>pablorodriguez</t>
+  </si>
+  <si>
+    <t>pablo.rodriguez@email.com</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>90123457</t>
+  </si>
+  <si>
+    <t>987654369</t>
+  </si>
+  <si>
+    <t>marcosjimenez</t>
+  </si>
+  <si>
+    <t>marcos.jimenez@email.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>P901234569</t>
+  </si>
+  <si>
+    <t>987654370</t>
+  </si>
+  <si>
+    <t>silviaperez</t>
+  </si>
+  <si>
+    <t>silvia.perez@email.com</t>
   </si>
 </sst>
 </file>
@@ -110,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -182,6 +1046,1427 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30" t="s">
+        <v>185</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" t="s">
+        <v>198</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>204</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
+        <v>210</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" t="s">
+        <v>215</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>216</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" t="s">
+        <v>222</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
+        <v>226</v>
+      </c>
+      <c r="E37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38" t="s">
+        <v>232</v>
+      </c>
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" t="s">
+        <v>233</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>239</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>241</v>
+      </c>
+      <c r="B40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
+        <v>245</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>247</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>250</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>254</v>
+      </c>
+      <c r="E42" t="s">
+        <v>255</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
+        <v>256</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>258</v>
+      </c>
+      <c r="B43" t="s">
+        <v>259</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>260</v>
+      </c>
+      <c r="E43" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>262</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>264</v>
+      </c>
+      <c r="B44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>273</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>275</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" t="s">
+        <v>277</v>
+      </c>
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>282</v>
+      </c>
+      <c r="E47" t="s">
+        <v>283</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>284</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>206</v>
+      </c>
+      <c r="B48" t="s">
+        <v>286</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" t="s">
+        <v>289</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
+        <v>292</v>
+      </c>
+      <c r="E49" t="s">
+        <v>293</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>294</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>296</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>297</v>
+      </c>
+      <c r="E50" t="s">
+        <v>298</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" t="s">
+        <v>299</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" t="s">
+        <v>302</v>
+      </c>
+      <c r="E51" t="s">
+        <v>303</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>304</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
+++ b/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="319">
   <si>
     <t>Nombres</t>
   </si>
@@ -930,6 +930,45 @@
   </si>
   <si>
     <t>silvia.perez@email.com</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>242525</t>
+  </si>
+  <si>
+    <t>2424242</t>
+  </si>
+  <si>
+    <t>orrai vagazo</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>fgfgfg</t>
+  </si>
+  <si>
+    <t>dsd</t>
+  </si>
+  <si>
+    <t>sdsds</t>
+  </si>
+  <si>
+    <t>21212</t>
+  </si>
+  <si>
+    <t>44747</t>
+  </si>
+  <si>
+    <t>jacky</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>12121212</t>
   </si>
 </sst>
 </file>
@@ -974,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -2467,6 +2506,64 @@
         <v>305</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" t="s">
+        <v>306</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>307</v>
+      </c>
+      <c r="E52" t="s">
+        <v>308</v>
+      </c>
+      <c r="F52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" t="s">
+        <v>309</v>
+      </c>
+      <c r="H52" t="s">
+        <v>310</v>
+      </c>
+      <c r="I52" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>312</v>
+      </c>
+      <c r="B53" t="s">
+        <v>313</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="s">
+        <v>314</v>
+      </c>
+      <c r="E53" t="s">
+        <v>315</v>
+      </c>
+      <c r="F53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" t="s">
+        <v>316</v>
+      </c>
+      <c r="H53" t="s">
+        <v>317</v>
+      </c>
+      <c r="I53" t="s">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
+++ b/ProyectoAsistencia/ReporteRegistrosUsuarios.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <si>
     <t>Nombres</t>
   </si>
@@ -41,70 +41,124 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>Víctor</t>
-  </si>
-  <si>
-    <t>Salazar</t>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>DNI</t>
+  </si>
+  <si>
+    <t>12345678</t>
+  </si>
+  <si>
+    <t>987654321</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>juanperez</t>
+  </si>
+  <si>
+    <t>pass123</t>
+  </si>
+  <si>
+    <t>juan.perez@email.com</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Ramírez</t>
+  </si>
+  <si>
+    <t>67890123</t>
+  </si>
+  <si>
+    <t>987654331</t>
+  </si>
+  <si>
+    <t>DOCENTE</t>
+  </si>
+  <si>
+    <t>saramirez</t>
+  </si>
+  <si>
+    <t>sara.ramirez@email.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>Álvarez</t>
+  </si>
+  <si>
+    <t>89012345</t>
+  </si>
+  <si>
+    <t>987654335</t>
+  </si>
+  <si>
+    <t>carmenalvarez</t>
+  </si>
+  <si>
+    <t>carmen.alvarez@email.com</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>Suárez</t>
   </si>
   <si>
     <t>PASAPORTE</t>
   </si>
   <si>
-    <t>P789012346</t>
-  </si>
-  <si>
-    <t>987654350</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>victorsalazar</t>
-  </si>
-  <si>
-    <t>pass123</t>
-  </si>
-  <si>
-    <t>victor.salazar@email.com</t>
-  </si>
-  <si>
-    <t>Verónica</t>
-  </si>
-  <si>
-    <t>Luna</t>
-  </si>
-  <si>
-    <t>DNI</t>
-  </si>
-  <si>
-    <t>89012346</t>
-  </si>
-  <si>
-    <t>987654353</t>
-  </si>
-  <si>
-    <t>DOCENTE</t>
-  </si>
-  <si>
-    <t>veronicaluna</t>
-  </si>
-  <si>
-    <t>veronica.luna@email.com</t>
-  </si>
-  <si>
-    <t>Morales</t>
-  </si>
-  <si>
-    <t>78901236</t>
-  </si>
-  <si>
-    <t>987654367</t>
-  </si>
-  <si>
-    <t>veronicamorales</t>
-  </si>
-  <si>
-    <t>veronica.morales@email.com</t>
+    <t>P890123456</t>
+  </si>
+  <si>
+    <t>987654338</t>
+  </si>
+  <si>
+    <t>manuelsuarez</t>
+  </si>
+  <si>
+    <t>manuel.suarez@email.com</t>
+  </si>
+  <si>
+    <t>Tomás</t>
+  </si>
+  <si>
+    <t>Gutiérrez</t>
+  </si>
+  <si>
+    <t>P890123457</t>
+  </si>
+  <si>
+    <t>987654352</t>
+  </si>
+  <si>
+    <t>tomasgutierrez</t>
+  </si>
+  <si>
+    <t>tomas.gutierrez@email.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>P901234569</t>
+  </si>
+  <si>
+    <t>987654370</t>
+  </si>
+  <si>
+    <t>silviaperez</t>
+  </si>
+  <si>
+    <t>silvia.perez@email.com</t>
   </si>
 </sst>
 </file>
@@ -149,7 +203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -229,36 +283,36 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -267,7 +321,7 @@
         <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -277,6 +331,93 @@
       </c>
       <c r="I4" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
